--- a/data/trans_bre/IP04D$aparatos-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$aparatos-Habitat-trans_bre.xlsx
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 15,62</t>
+          <t>-4,5; 14,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,99; 6,43</t>
+          <t>-13,12; 7,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 23,05</t>
+          <t>-5,64; 24,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 26,16</t>
+          <t>-5,68; 23,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-23,36; 12,9</t>
+          <t>-22,05; 14,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 48,99</t>
+          <t>-8,4; 55,1</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,9; 4,43</t>
+          <t>-10,24; 4,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 7,46</t>
+          <t>-8,21; 7,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,22; 4,77</t>
+          <t>-13,33; 5,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,26; 7,17</t>
+          <t>-14,65; 6,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-13,43; 15,03</t>
+          <t>-14,42; 14,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,43; 7,86</t>
+          <t>-19,35; 9,44</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 12,33</t>
+          <t>-3,51; 12,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 11,22</t>
+          <t>-5,63; 12,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,48; 27,45</t>
+          <t>2,07; 27,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 19,43</t>
+          <t>-5,08; 20,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,26; 30,64</t>
+          <t>-11,54; 33,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 53,32</t>
+          <t>3,54; 52,83</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 13,68</t>
+          <t>-3,58; 13,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,14; 4,66</t>
+          <t>-11,7; 5,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 11,57</t>
+          <t>-6,87; 11,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 29,55</t>
+          <t>-6,37; 29,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-19,55; 9,2</t>
+          <t>-19,14; 9,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,89; 25,27</t>
+          <t>-12,36; 25,7</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 6,85</t>
+          <t>-1,7; 6,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 3,28</t>
+          <t>-5,33; 3,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 10,58</t>
+          <t>-0,98; 10,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 11,36</t>
+          <t>-2,67; 11,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 6,34</t>
+          <t>-9,54; 6,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 19,01</t>
+          <t>-1,53; 17,69</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04D$aparatos-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$aparatos-Habitat-trans_bre.xlsx
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 14,26</t>
+          <t>-3,42; 14,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,12; 7,12</t>
+          <t>-12,56; 6,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 24,73</t>
+          <t>-5,58; 22,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 23,49</t>
+          <t>-5,17; 24,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-22,05; 14,03</t>
+          <t>-21,44; 13,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 55,1</t>
+          <t>-8,24; 45,45</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-10,24; 4,31</t>
+          <t>-10,19; 4,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,21; 7,28</t>
+          <t>-7,79; 7,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,33; 5,96</t>
+          <t>-11,54; 5,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,65; 6,75</t>
+          <t>-14,32; 7,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,42; 14,56</t>
+          <t>-13,58; 14,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,35; 9,44</t>
+          <t>-16,87; 9,81</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 12,82</t>
+          <t>-3,92; 12,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 12,46</t>
+          <t>-5,62; 11,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,07; 27,05</t>
+          <t>0,54; 25,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 20,85</t>
+          <t>-5,55; 19,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,54; 33,22</t>
+          <t>-12,11; 31,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,54; 52,83</t>
+          <t>0,91; 50,96</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 13,41</t>
+          <t>-3,07; 13,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,7; 5,5</t>
+          <t>-11,18; 5,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 11,84</t>
+          <t>-6,78; 11,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 29,46</t>
+          <t>-5,72; 29,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-19,14; 9,94</t>
+          <t>-18,64; 9,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,36; 25,7</t>
+          <t>-12,14; 23,94</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 6,83</t>
+          <t>-1,89; 6,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 3,13</t>
+          <t>-5,19; 3,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 10,02</t>
+          <t>-1,82; 10,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 11,48</t>
+          <t>-2,95; 10,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,54; 6,3</t>
+          <t>-9,56; 6,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 17,69</t>
+          <t>-3,23; 18,16</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04D$aparatos-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$aparatos-Habitat-trans_bre.xlsx
@@ -518,8 +518,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que no dispone de instalación de calefacción en su vivienda pero sí tiene aparatos de calefacción</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -604,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,74</t>
+          <t>4,35</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -619,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -632,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 14,95</t>
+          <t>-2,94; 15,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,56; 6,96</t>
+          <t>-13,99; 6,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 22,16</t>
+          <t>-7,26; 19,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 24,07</t>
+          <t>-4,19; 26,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-21,44; 13,96</t>
+          <t>-23,36; 12,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 45,45</t>
+          <t>-10,73; 37,2</t>
         </is>
       </c>
     </row>
@@ -684,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-3,0</t>
+          <t>-2,46</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -699,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-4,65%</t>
+          <t>-3,71%</t>
         </is>
       </c>
     </row>
@@ -712,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-10,19; 4,81</t>
+          <t>-9,9; 4,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 7,51</t>
+          <t>-7,75; 7,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,54; 5,96</t>
+          <t>-11,22; 5,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,32; 7,8</t>
+          <t>-14,26; 7,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-13,58; 14,99</t>
+          <t>-13,43; 15,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-16,87; 9,81</t>
+          <t>-16,01; 8,34</t>
         </is>
       </c>
     </row>
@@ -764,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11,97</t>
+          <t>8,09</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -779,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>13,85%</t>
         </is>
       </c>
     </row>
@@ -792,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 12,21</t>
+          <t>-4,62; 12,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 11,96</t>
+          <t>-6,63; 11,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 25,96</t>
+          <t>-1,01; 17,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 19,69</t>
+          <t>-6,69; 19,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,11; 31,68</t>
+          <t>-14,26; 30,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 50,96</t>
+          <t>-1,52; 34,32</t>
         </is>
       </c>
     </row>
@@ -844,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,44</t>
+          <t>2,5</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -859,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -872,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 13,68</t>
+          <t>-2,74; 13,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,18; 5,06</t>
+          <t>-12,14; 4,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 11,09</t>
+          <t>-6,74; 12,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 29,63</t>
+          <t>-5,26; 29,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-18,64; 9,49</t>
+          <t>-19,55; 9,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,14; 23,94</t>
+          <t>-12,09; 25,76</t>
         </is>
       </c>
     </row>
@@ -924,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,91</t>
+          <t>2,31</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -939,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -952,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 6,38</t>
+          <t>-1,47; 6,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 3,16</t>
+          <t>-5,23; 3,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 10,24</t>
+          <t>-2,29; 7,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 10,56</t>
+          <t>-2,35; 11,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 6,12</t>
+          <t>-9,61; 6,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 18,16</t>
+          <t>-3,68; 12,79</t>
         </is>
       </c>
     </row>
